--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E46575AF-9D41-4276-AAA4-2DA9B3245A67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06751D06-282E-437D-92F9-E11556222798}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90886884-6E90-42EE-B004-8657DE25F56C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17961BA7-E5D2-4B3D-BBB8-BB7E1CFD0343}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A5DCD00-D4A7-4A6E-ACD0-35CCB2B8852E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB202D2-E13A-4361-A31E-F806306CE3E4}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06751D06-282E-437D-92F9-E11556222798}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D743A419-3138-44F8-880E-C4EADE5D5457}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17961BA7-E5D2-4B3D-BBB8-BB7E1CFD0343}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E00D825D-AA31-47E1-A23F-F293EBAB2D8D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB202D2-E13A-4361-A31E-F806306CE3E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{231220AA-6A2B-4A8C-A67A-4728B25B71EA}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D743A419-3138-44F8-880E-C4EADE5D5457}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990D45E4-102C-4423-B13C-84B43C0AD2EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E00D825D-AA31-47E1-A23F-F293EBAB2D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3515938-131A-4D80-A4AC-D9A091207AA3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{231220AA-6A2B-4A8C-A67A-4728B25B71EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC254EED-BE38-40AF-ABFC-F306DC20E7CC}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990D45E4-102C-4423-B13C-84B43C0AD2EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18AE5864-691F-4939-AE54-20BC48575960}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3515938-131A-4D80-A4AC-D9A091207AA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C85D74B-4162-47EE-93BD-414D23D5A5C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC254EED-BE38-40AF-ABFC-F306DC20E7CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9B4292-8AF9-48FC-B1A3-E2ED144E7798}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18AE5864-691F-4939-AE54-20BC48575960}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D73563DA-F27D-4201-B80B-5564D353702C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C85D74B-4162-47EE-93BD-414D23D5A5C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EBDE5C3-DAE6-46F7-8561-4287D4E2C1C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9B4292-8AF9-48FC-B1A3-E2ED144E7798}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A40C2073-2080-41A1-812B-F753F9A81CEB}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1428,22 +1428,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990D45E4-102C-4423-B13C-84B43C0AD2EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A6C946-46FC-45DF-A721-16B009CC5786}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3515938-131A-4D80-A4AC-D9A091207AA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9672CAF3-3501-4ECF-B853-15F75A4582C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC254EED-BE38-40AF-ABFC-F306DC20E7CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7547355-9601-40E4-AB16-BE834CBD0092}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1428,22 +1428,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D73563DA-F27D-4201-B80B-5564D353702C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AE16A30-CDEA-44C8-BC36-605A6A006E0B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EBDE5C3-DAE6-46F7-8561-4287D4E2C1C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{545018D9-D618-4C0E-8B8D-73CDDC59D10F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A40C2073-2080-41A1-812B-F753F9A81CEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DEEA11-7970-44F9-BB3A-12E21C1D3FB5}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AE16A30-CDEA-44C8-BC36-605A6A006E0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6253FA66-9C20-4970-8754-98D76C4C3872}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{545018D9-D618-4C0E-8B8D-73CDDC59D10F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B034BB37-9430-4B54-B637-987D3F113FEC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DEEA11-7970-44F9-BB3A-12E21C1D3FB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B056BC3E-8A17-42C7-A28D-2D7035ED30F7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6253FA66-9C20-4970-8754-98D76C4C3872}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33918FD5-3F18-407B-B9E0-660E26C1A4AC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B034BB37-9430-4B54-B637-987D3F113FEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{876056EA-678C-474E-8004-F5BBB408D1ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B056BC3E-8A17-42C7-A28D-2D7035ED30F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F55F056-EE75-4B8D-AE8D-E55B61BDDDBA}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33918FD5-3F18-407B-B9E0-660E26C1A4AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2B477F2-46EC-43B6-B7FF-7B9A799E0EEB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{876056EA-678C-474E-8004-F5BBB408D1ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B7B6AC-C5FD-4CB8-9F2F-56436BD6AF8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F55F056-EE75-4B8D-AE8D-E55B61BDDDBA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4685597F-4B20-42F4-B8D1-55EC6987174E}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2B477F2-46EC-43B6-B7FF-7B9A799E0EEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C721D7D-520B-48DC-8426-7D96C2663FE2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B7B6AC-C5FD-4CB8-9F2F-56436BD6AF8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BFFCFA2-582B-48BA-9D2D-85AC0D38D1D6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4685597F-4B20-42F4-B8D1-55EC6987174E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C926192-5C06-4A13-820D-59420225ECA1}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C721D7D-520B-48DC-8426-7D96C2663FE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE8289A-CF61-4417-A320-F51BA698A3E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BFFCFA2-582B-48BA-9D2D-85AC0D38D1D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454B5D21-FBBD-47BC-97DF-84A912266C70}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C926192-5C06-4A13-820D-59420225ECA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F174B8EE-220E-4C66-9391-5B5CC8FB5583}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE8289A-CF61-4417-A320-F51BA698A3E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DADE54-F11A-4377-BD3B-11E11C594991}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454B5D21-FBBD-47BC-97DF-84A912266C70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B445CEC-298C-434F-BA86-E3EC40F11D16}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F174B8EE-220E-4C66-9391-5B5CC8FB5583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AB5F8D4-E6CA-41DB-91D5-ACD922B48288}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DADE54-F11A-4377-BD3B-11E11C594991}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA4C5FBD-D3BE-4288-A335-AD3A21EA899B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B445CEC-298C-434F-BA86-E3EC40F11D16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9057568D-2EAE-4617-B0A5-60D3E98AFBA3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AB5F8D4-E6CA-41DB-91D5-ACD922B48288}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F72B90A-D842-478B-9414-1C1D42D323E7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA4C5FBD-D3BE-4288-A335-AD3A21EA899B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D02CEB4-9438-4E41-9A41-AC6043D0C2C9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9057568D-2EAE-4617-B0A5-60D3E98AFBA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D71C0E-E70A-43A3-B967-6BA02122844C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F72B90A-D842-478B-9414-1C1D42D323E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4837C3-38FD-4A5D-95B1-44EC5135D2E0}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D02CEB4-9438-4E41-9A41-AC6043D0C2C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DE6C3A3-626D-42EA-BD24-B7A480DDB634}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D71C0E-E70A-43A3-B967-6BA02122844C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0047E91C-425F-49DA-B571-D45B7BA94FBC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4837C3-38FD-4A5D-95B1-44EC5135D2E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0683E7A4-2F1D-4AB2-9D3A-349FFE6D6A29}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DE6C3A3-626D-42EA-BD24-B7A480DDB634}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AD28714-6453-4AE2-B502-A27B1B4F4BDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0047E91C-425F-49DA-B571-D45B7BA94FBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{596445CF-36F3-466E-97FE-96DC2A44DC42}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0683E7A4-2F1D-4AB2-9D3A-349FFE6D6A29}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C853753-A87D-43BD-A1DA-F731FF65EC70}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AD28714-6453-4AE2-B502-A27B1B4F4BDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA4530AE-BE37-4A8C-80AE-4E2B40E62A07}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{596445CF-36F3-466E-97FE-96DC2A44DC42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33E090E3-2EEC-40B1-922D-1B284857CD34}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C853753-A87D-43BD-A1DA-F731FF65EC70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EC27760-78CA-4B73-85F7-EED40501C7C7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA4530AE-BE37-4A8C-80AE-4E2B40E62A07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{588FA65A-977C-40C7-90F0-54E9B589B420}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33E090E3-2EEC-40B1-922D-1B284857CD34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F2AFDF8-5B3E-43A0-9EAE-3DD3618B7155}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EC27760-78CA-4B73-85F7-EED40501C7C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52014DF7-E3FD-4390-91F0-7833B286026F}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{588FA65A-977C-40C7-90F0-54E9B589B420}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{859103CC-C168-4F50-9E39-9C4069F382E1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F2AFDF8-5B3E-43A0-9EAE-3DD3618B7155}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AF082EF-B8EE-45BA-8CCB-76DE2A697C75}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52014DF7-E3FD-4390-91F0-7833B286026F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FE14DC2-9DFF-4294-BEB0-C968EC9A3A08}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{859103CC-C168-4F50-9E39-9C4069F382E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76DFBAEB-8378-4D9A-931D-99E631B71F20}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AF082EF-B8EE-45BA-8CCB-76DE2A697C75}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CE8D7C8-4E25-4025-8BC0-AC4544DDB96B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FE14DC2-9DFF-4294-BEB0-C968EC9A3A08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B63F55-BAF5-46C9-BFF4-8700557A674D}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76DFBAEB-8378-4D9A-931D-99E631B71F20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A6C78AE-DA7B-4ECF-B961-E1A37BF346D8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CE8D7C8-4E25-4025-8BC0-AC4544DDB96B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A038B736-C9B5-4F13-A8DA-BE0E8965B3E7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B63F55-BAF5-46C9-BFF4-8700557A674D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18043B22-B96E-4378-BBBD-5F0E628A8237}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A6C78AE-DA7B-4ECF-B961-E1A37BF346D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D3D4061-BCB3-4B8B-95A5-E54CEDA45F58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A038B736-C9B5-4F13-A8DA-BE0E8965B3E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA89629-EBEB-4498-8412-91EE0B1105B5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18043B22-B96E-4378-BBBD-5F0E628A8237}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C95776-C183-4D33-A0B6-1348DC518FEC}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D3D4061-BCB3-4B8B-95A5-E54CEDA45F58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC14741E-790F-4016-9D47-80901154F5D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA89629-EBEB-4498-8412-91EE0B1105B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A4E79-B366-4A66-A2E3-190E57FE77A0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C95776-C183-4D33-A0B6-1348DC518FEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD4AFD13-E639-4E50-8281-89B2A5EA1439}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC14741E-790F-4016-9D47-80901154F5D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFCBC1F-3C47-4043-9C20-1BB134C3191D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A4E79-B366-4A66-A2E3-190E57FE77A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E1E4B6F-2C41-438D-A81A-4DBC477A04FE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD4AFD13-E639-4E50-8281-89B2A5EA1439}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6080BEF-2030-4759-905E-C47579028C7A}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_manyprimates.xlsx
@@ -1437,13 +1437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFCBC1F-3C47-4043-9C20-1BB134C3191D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9254EFAA-47C7-4058-9DF5-9F4E88234F5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E1E4B6F-2C41-438D-A81A-4DBC477A04FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41AF47A3-2063-472F-A5F7-5A0AC9161007}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6080BEF-2030-4759-905E-C47579028C7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED791E00-170C-40AF-8C9A-87A271BE308A}"/>
 </file>